--- a/策划/excel/20_BattleBuff.xlsx
+++ b/策划/excel/20_BattleBuff.xlsx
@@ -12,27 +12,192 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="200" formatCode="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0"/>
   </numFmts>
-  <fonts count="3">
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="10"/>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -41,16 +206,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7EDF3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34495E"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -58,65 +399,341 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns2:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -332,44 +949,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.571428298950195" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="24.285715103149414" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.714285850524902" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.285714149475098" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.285714149475098" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.571428298950195" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="21.428571701049805" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="67.14286041259766" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.752380952381" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13.247619047619" customWidth="1"/>
+    <col min="4" max="4" width="13.247619047619" customWidth="1"/>
+    <col min="5" max="5" width="13.247619047619" customWidth="1"/>
+    <col min="6" max="6" width="14.2857142857143" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="165.857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="str">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="7" t="str">
         <v>编号【KEY】</v>
       </c>
-      <c r="B1" s="10" t="str">
+      <c r="B1" s="8" t="str">
         <v>状态枚举</v>
       </c>
-      <c r="C1" s="10" t="str">
+      <c r="C1" s="8" t="str">
         <v>状态名称</v>
       </c>
-      <c r="D1" s="10" t="str">
+      <c r="D1" s="8" t="str">
         <v>状态分类</v>
       </c>
-      <c r="E1" s="10" t="str">
+      <c r="E1" s="8" t="str">
         <v>叠加方式</v>
       </c>
-      <c r="F1" s="10" t="str">
+      <c r="F1" s="8" t="str">
         <v>最大层数</v>
       </c>
-      <c r="G1" s="10" t="str">
+      <c r="G1" s="8" t="str">
         <v>默认回合末衰减</v>
       </c>
-      <c r="H1" s="10" t="str">
+      <c r="H1" s="8" t="str">
         <v>效果说明</v>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="8" t="str">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="str">
         <v>id</v>
       </c>
       <c r="B2" s="8" t="str">
@@ -394,8 +1011,8 @@
         <v>description</v>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="8" t="str">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="str">
         <v>int</v>
       </c>
       <c r="B3" s="8" t="str">
@@ -420,8 +1037,8 @@
         <v>string</v>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="str">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="str">
         <v>server</v>
       </c>
       <c r="B4" s="8" t="str">
@@ -446,8 +1063,8 @@
         <v>server</v>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="8" t="str">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="str">
         <v>client</v>
       </c>
       <c r="B5" s="8" t="str">
@@ -472,523 +1089,523 @@
         <v>client</v>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="11" t="n">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="n">
         <v>200001</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="10" t="str">
         <v>STRENGTH</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="10" t="str">
         <v>力量</v>
       </c>
-      <c r="D6" s="6" t="str">
+      <c r="D6" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E6" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G6" s="7" t="b">
+      <c r="E6" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G6" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="11" t="str">
         <v>每层增加1点攻击伤害，可为负数</v>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="11" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="n">
         <v>200002</v>
       </c>
-      <c r="B7" s="6" t="str">
+      <c r="B7" s="10" t="str">
         <v>DEXTERITY</v>
       </c>
-      <c r="C7" s="6" t="str">
+      <c r="C7" s="10" t="str">
         <v>敏捷</v>
       </c>
-      <c r="D7" s="6" t="str">
+      <c r="D7" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E7" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G7" s="7" t="b">
+      <c r="E7" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G7" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="str">
+      <c r="H7" s="11" t="str">
         <v>每层增加1点获得的格挡，可为负数</v>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="11" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="n">
         <v>200003</v>
       </c>
-      <c r="B8" s="6" t="str">
+      <c r="B8" s="10" t="str">
         <v>WEAK</v>
       </c>
-      <c r="C8" s="6" t="str">
+      <c r="C8" s="10" t="str">
         <v>虚弱</v>
       </c>
-      <c r="D8" s="6" t="str">
+      <c r="D8" s="10" t="str">
         <v>DEBUFF</v>
       </c>
-      <c r="E8" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G8" s="7" t="b">
+      <c r="E8" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G8" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="6" t="str">
+      <c r="H8" s="11" t="str">
         <v>攻击伤害降低25%，默认持续范围每回合减少1层</v>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="11" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="n">
         <v>200004</v>
       </c>
-      <c r="B9" s="6" t="str">
+      <c r="B9" s="10" t="str">
         <v>VULNERABLE</v>
       </c>
-      <c r="C9" s="6" t="str">
+      <c r="C9" s="10" t="str">
         <v>易伤</v>
       </c>
-      <c r="D9" s="6" t="str">
+      <c r="D9" s="10" t="str">
         <v>DEBUFF</v>
       </c>
-      <c r="E9" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G9" s="7" t="b">
+      <c r="E9" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G9" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="6" t="str">
+      <c r="H9" s="11" t="str">
         <v>受到的攻击伤害提高50%，默认持续范围每回合减少1层</v>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="11" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="n">
         <v>200005</v>
       </c>
-      <c r="B10" s="6" t="str">
+      <c r="B10" s="10" t="str">
         <v>FRAIL</v>
       </c>
-      <c r="C10" s="6" t="str">
+      <c r="C10" s="10" t="str">
         <v>脆弱</v>
       </c>
-      <c r="D10" s="6" t="str">
+      <c r="D10" s="10" t="str">
         <v>DEBUFF</v>
       </c>
-      <c r="E10" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G10" s="7" t="b">
+      <c r="E10" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G10" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="6" t="str">
+      <c r="H10" s="11" t="str">
         <v>获得的格挡降低25%，默认持续范围每回合减少1层</v>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="11" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="n">
         <v>200006</v>
       </c>
-      <c r="B11" s="6" t="str">
+      <c r="B11" s="10" t="str">
         <v>POISON</v>
       </c>
-      <c r="C11" s="6" t="str">
+      <c r="C11" s="10" t="str">
         <v>中毒</v>
       </c>
-      <c r="D11" s="6" t="str">
+      <c r="D11" s="10" t="str">
         <v>DEBUFF</v>
       </c>
-      <c r="E11" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G11" s="7" t="b">
+      <c r="E11" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G11" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="6" t="str">
+      <c r="H11" s="11" t="str">
         <v>回合开始失去等同层数的生命，结算后减少1层</v>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="11" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="n">
         <v>200007</v>
       </c>
-      <c r="B12" s="6" t="str">
+      <c r="B12" s="10" t="str">
         <v>ARTIFACT</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C12" s="10" t="str">
         <v>人工制品</v>
       </c>
-      <c r="D12" s="6" t="str">
+      <c r="D12" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E12" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G12" s="7" t="b">
+      <c r="E12" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G12" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="str">
+      <c r="H12" s="11" t="str">
         <v>抵消一次施加减益，消耗1层</v>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="11" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="n">
         <v>200008</v>
       </c>
-      <c r="B13" s="6" t="str">
+      <c r="B13" s="10" t="str">
         <v>INTANGIBLE</v>
       </c>
-      <c r="C13" s="6" t="str">
+      <c r="C13" s="10" t="str">
         <v>无实体</v>
       </c>
-      <c r="D13" s="6" t="str">
+      <c r="D13" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E13" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G13" s="7" t="b">
+      <c r="E13" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G13" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="6" t="str">
+      <c r="H13" s="11" t="str">
         <v>非生命损失伤害最多为1，默认持续范围每回合减少1层</v>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="11" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="n">
         <v>200009</v>
       </c>
-      <c r="B14" s="6" t="str">
+      <c r="B14" s="10" t="str">
         <v>THORNS</v>
       </c>
-      <c r="C14" s="6" t="str">
+      <c r="C14" s="10" t="str">
         <v>荆棘</v>
       </c>
-      <c r="D14" s="6" t="str">
+      <c r="D14" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E14" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G14" s="7" t="b">
+      <c r="E14" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G14" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="str">
+      <c r="H14" s="11" t="str">
         <v>受到攻击后向攻击方造成等同层数的反击伤害</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="11" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="n">
         <v>200010</v>
       </c>
-      <c r="B15" s="6" t="str">
+      <c r="B15" s="10" t="str">
         <v>REGENERATION</v>
       </c>
-      <c r="C15" s="6" t="str">
+      <c r="C15" s="10" t="str">
         <v>再生</v>
       </c>
-      <c r="D15" s="6" t="str">
+      <c r="D15" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E15" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G15" s="7" t="b">
+      <c r="E15" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G15" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="str">
+      <c r="H15" s="11" t="str">
         <v>回合结束回复等同层数的生命，然后减少1层</v>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="11" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="n">
         <v>200011</v>
       </c>
-      <c r="B16" s="6" t="str">
+      <c r="B16" s="10" t="str">
         <v>METALLICIZE</v>
       </c>
-      <c r="C16" s="6" t="str">
+      <c r="C16" s="10" t="str">
         <v>金属化</v>
       </c>
-      <c r="D16" s="6" t="str">
+      <c r="D16" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E16" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G16" s="7" t="b">
+      <c r="E16" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G16" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="str">
+      <c r="H16" s="11" t="str">
         <v>回合结束获得等同层数的格挡</v>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="11" t="n">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="n">
         <v>200012</v>
       </c>
-      <c r="B17" s="6" t="str">
+      <c r="B17" s="10" t="str">
         <v>BARRICADE</v>
       </c>
-      <c r="C17" s="6" t="str">
+      <c r="C17" s="10" t="str">
         <v>壁垒</v>
       </c>
-      <c r="D17" s="6" t="str">
+      <c r="D17" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E17" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G17" s="7" t="b">
+      <c r="E17" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G17" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="6" t="str">
+      <c r="H17" s="11" t="str">
         <v>回合开始保留格挡</v>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="11" t="n">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="n">
         <v>200013</v>
       </c>
-      <c r="B18" s="6" t="str">
+      <c r="B18" s="10" t="str">
         <v>ARMOR</v>
       </c>
-      <c r="C18" s="6" t="str">
+      <c r="C18" s="10" t="str">
         <v>硬甲</v>
       </c>
-      <c r="D18" s="6" t="str">
+      <c r="D18" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E18" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G18" s="7" t="b">
+      <c r="E18" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G18" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="str">
+      <c r="H18" s="11" t="str">
         <v>每层抵消1点非生命损失伤害</v>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="11" t="n">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="n">
         <v>200014</v>
       </c>
-      <c r="B19" s="6" t="str">
+      <c r="B19" s="10" t="str">
         <v>EVASION</v>
       </c>
-      <c r="C19" s="6" t="str">
+      <c r="C19" s="10" t="str">
         <v>闪避</v>
       </c>
-      <c r="D19" s="6" t="str">
+      <c r="D19" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E19" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G19" s="7" t="b">
+      <c r="E19" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="6" t="str">
+      <c r="H19" s="11" t="str">
         <v>抵消一次攻击，消耗1层</v>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="11" t="n">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="n">
         <v>200015</v>
       </c>
-      <c r="B20" s="6" t="str">
+      <c r="B20" s="10" t="str">
         <v>FLIGHT</v>
       </c>
-      <c r="C20" s="6" t="str">
+      <c r="C20" s="10" t="str">
         <v>飞行</v>
       </c>
-      <c r="D20" s="6" t="str">
+      <c r="D20" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E20" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G20" s="7" t="b">
+      <c r="E20" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G20" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="str">
+      <c r="H20" s="11" t="str">
         <v>受到攻击伤害减半，攻击造成生命损失后减少1层</v>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="11" t="n">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="n">
         <v>200016</v>
       </c>
-      <c r="B21" s="6" t="str">
+      <c r="B21" s="10" t="str">
         <v>PLATED_ARMOR</v>
       </c>
-      <c r="C21" s="6" t="str">
+      <c r="C21" s="10" t="str">
         <v>多层护甲</v>
       </c>
-      <c r="D21" s="6" t="str">
+      <c r="D21" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E21" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G21" s="7" t="b">
+      <c r="E21" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G21" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="6" t="str">
+      <c r="H21" s="11" t="str">
         <v>回合结束获得格挡，攻击造成生命损失后减少1层</v>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="11" t="n">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="n">
         <v>200017</v>
       </c>
-      <c r="B22" s="6" t="str">
+      <c r="B22" s="10" t="str">
         <v>FURY</v>
       </c>
-      <c r="C22" s="6" t="str">
+      <c r="C22" s="10" t="str">
         <v>受击暴怒</v>
       </c>
-      <c r="D22" s="6" t="str">
+      <c r="D22" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E22" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G22" s="7" t="b">
+      <c r="E22" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G22" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H22" s="6" t="str">
+      <c r="H22" s="11" t="str">
         <v>攻击造成生命损失后，获得等同层数的力量</v>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="11" t="n">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="n">
         <v>200018</v>
       </c>
-      <c r="B23" s="6" t="str">
+      <c r="B23" s="10" t="str">
         <v>RITUAL</v>
       </c>
-      <c r="C23" s="6" t="str">
+      <c r="C23" s="10" t="str">
         <v>仪式</v>
       </c>
-      <c r="D23" s="6" t="str">
+      <c r="D23" s="10" t="str">
         <v>BUFF</v>
       </c>
-      <c r="E23" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G23" s="7" t="b">
+      <c r="E23" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G23" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H23" s="6" t="str">
+      <c r="H23" s="11" t="str">
         <v>回合结束获得等同层数的力量</v>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="11" t="n">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="9" t="n">
         <v>200019</v>
       </c>
-      <c r="B24" s="6" t="str">
+      <c r="B24" s="10" t="str">
         <v>BURN</v>
       </c>
-      <c r="C24" s="6" t="str">
+      <c r="C24" s="10" t="str">
         <v>灼烧</v>
       </c>
-      <c r="D24" s="6" t="str">
+      <c r="D24" s="10" t="str">
         <v>DEBUFF</v>
       </c>
-      <c r="E24" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G24" s="7" t="b">
+      <c r="E24" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G24" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="6" t="str">
+      <c r="H24" s="11" t="str">
         <v>回合结束失去等同层数的生命，然后减少1层</v>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="11" t="n">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="n">
         <v>200020</v>
       </c>
-      <c r="B25" s="6" t="str">
+      <c r="B25" s="10" t="str">
         <v>CONSTRICTED</v>
       </c>
-      <c r="C25" s="6" t="str">
+      <c r="C25" s="10" t="str">
         <v>紧缚</v>
       </c>
-      <c r="D25" s="6" t="str">
+      <c r="D25" s="10" t="str">
         <v>DEBUFF</v>
       </c>
-      <c r="E25" s="6" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="G25" s="7" t="b">
+      <c r="E25" s="10" t="str">
+        <v>ADD</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G25" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H25" s="6" t="str">
+      <c r="H25" s="11" t="str">
         <v>回合结束失去等同层数的生命，然后减少1层</v>
       </c>
     </row>
